--- a/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T21:11:11+00:00</t>
+    <t>2024-10-11T21:22:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T21:22:03+00:00</t>
+    <t>2024-10-14T20:42:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-14T20:42:47+00:00</t>
+    <t>2024-10-15T22:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-15T22:40:43+00:00</t>
+    <t>2024-10-17T22:00:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-17T22:00:52+00:00</t>
+    <t>2024-10-21T13:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T13:09:55+00:00</t>
+    <t>2024-10-22T13:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/TDDUI_ExempleCasUsage_SSIAD/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T13:49:16+00:00</t>
+    <t>2024-10-24T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
